--- a/mistral_translate_work/split_by_prompt/excel/ui/lang_multi_text/lang_multi_text__ui__part_0002.xlsx
+++ b/mistral_translate_work/split_by_prompt/excel/ui/lang_multi_text/lang_multi_text__ui__part_0002.xlsx
@@ -5449,7 +5449,7 @@
       </c>
       <c r="M77" t="inlineStr">
         <is>
-          <t>Activated</t>
+          <t>Đã kích hoạt</t>
         </is>
       </c>
     </row>
@@ -13249,7 +13249,7 @@
       </c>
       <c r="M197" t="inlineStr">
         <is>
-          <t>Switch</t>
+          <t>Chuyển đổi</t>
         </is>
       </c>
     </row>
@@ -13574,7 +13574,7 @@
       </c>
       <c r="M202" t="inlineStr">
         <is>
-          <t>Loại tinh nhuệ</t>
+          <t>Cấp Tinh Anh</t>
         </is>
       </c>
     </row>
@@ -14679,7 +14679,7 @@
       </c>
       <c r="M219" t="inlineStr">
         <is>
-          <t>General</t>
+          <t>Chung</t>
         </is>
       </c>
     </row>
@@ -16304,7 +16304,7 @@
       </c>
       <c r="M244" t="inlineStr">
         <is>
-          <t>Completed</t>
+          <t>Đã hoàn thành</t>
         </is>
       </c>
     </row>
@@ -16499,7 +16499,7 @@
       </c>
       <c r="M247" t="inlineStr">
         <is>
-          <t>Search</t>
+          <t>Tìm kiếm</t>
         </is>
       </c>
     </row>
@@ -19749,7 +19749,7 @@
       </c>
       <c r="M297" t="inlineStr">
         <is>
-          <t>Pause</t>
+          <t>Tạm dừng</t>
         </is>
       </c>
     </row>
@@ -29239,7 +29239,7 @@
       </c>
       <c r="M443" t="inlineStr">
         <is>
-          <t>Progress</t>
+          <t>Tiến độ</t>
         </is>
       </c>
     </row>
@@ -31839,7 +31839,7 @@
       </c>
       <c r="M483" t="inlineStr">
         <is>
-          <t>Exit</t>
+          <t>Thoát</t>
         </is>
       </c>
     </row>
